--- a/leads.xlsx
+++ b/leads.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\lead_gen_ai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E3265B-3AB3-4E1E-B380-A6B1DB741E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163E4BBD-D293-4C93-AE06-1597619B8C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="85">
   <si>
     <t>website</t>
   </si>
@@ -227,6 +227,54 @@
   </si>
   <si>
     <t>contact@hdwebsoft.com</t>
+  </si>
+  <si>
+    <t>https://vicsguide.com/european-startups-interested-in-vietnams-tech-industry/</t>
+  </si>
+  <si>
+    <t>info@vicsguide.com</t>
+  </si>
+  <si>
+    <t>0904111954</t>
+  </si>
+  <si>
+    <t>https://10times.com/company/hawa-corporation</t>
+  </si>
+  <si>
+    <t>0814118824</t>
+  </si>
+  <si>
+    <t>https://hblabgroup.com/ai-outsourcing-company-in-vietnam/</t>
+  </si>
+  <si>
+    <t>contact@hblab.vn, cs_gl@hblab.vn</t>
+  </si>
+  <si>
+    <t>0983098304, 0362819068</t>
+  </si>
+  <si>
+    <t>https://topsoftwarecompanies.co/ai-development/agencies/vietnam</t>
+  </si>
+  <si>
+    <t>0915051698, 0839956849</t>
+  </si>
+  <si>
+    <t>https://www.investasian.com/frontier-market/tech-startups-vietnam/</t>
+  </si>
+  <si>
+    <t>admin@investasian.com</t>
+  </si>
+  <si>
+    <t>0734561616</t>
+  </si>
+  <si>
+    <t>https://vndetective.com/</t>
+  </si>
+  <si>
+    <t>piinvietnam@gmail.com</t>
+  </si>
+  <si>
+    <t>0969651115, 0912933971</t>
   </si>
 </sst>
 </file>
@@ -242,12 +290,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -262,8 +316,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -566,372 +626,452 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="64.5546875" customWidth="1"/>
-    <col min="2" max="2" width="62.5546875" customWidth="1"/>
-    <col min="3" max="3" width="53.109375" customWidth="1"/>
+    <col min="1" max="1" width="44.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="46.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="42.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.77734375" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>9090909090</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>313534747</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="D10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="D12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="D13" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="D15" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="D18" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="D19" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="D20" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="D21" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="D22" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="D23" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="D25" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="D26" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="D28" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>17</v>
       </c>
     </row>
